--- a/report_templates/Payment Status.xlsx
+++ b/report_templates/Payment Status.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git hub repositeries\GRP_SYS\report_templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3b68409331e52ac1/Documents/GRP/GRP_SYS/report_templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF55236C-2425-464B-AFCF-50EEAAF32BAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{AF55236C-2425-464B-AFCF-50EEAAF32BAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55E6B1FE-3271-4CED-98AE-DFE3E495A70C}"/>
   <bookViews>
-    <workbookView xWindow="1830" yWindow="2660" windowWidth="23770" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,9 +38,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
-    <t>W.O.</t>
-  </si>
-  <si>
     <t>INSTA.</t>
   </si>
   <si>
@@ -59,7 +56,10 @@
     <t>REMARKS</t>
   </si>
   <si>
-    <t>SALES PER.</t>
+    <t>W.O.NO.</t>
+  </si>
+  <si>
+    <t>SALES PERSON</t>
   </si>
 </sst>
 </file>
@@ -104,12 +104,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -123,10 +138,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -144,6 +159,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -412,40 +431,40 @@
   <dimension ref="A1:H49"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.453125" customWidth="1"/>
+    <col min="1" max="1" width="8.81640625" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="3" width="11.7265625" customWidth="1"/>
     <col min="4" max="4" width="11.54296875" customWidth="1"/>
     <col min="5" max="5" width="11.7265625" customWidth="1"/>
     <col min="6" max="6" width="14.81640625" customWidth="1"/>
-    <col min="7" max="7" width="11.1796875" customWidth="1"/>
-    <col min="8" max="8" width="18.453125" customWidth="1"/>
+    <col min="7" max="7" width="15.1796875" customWidth="1"/>
+    <col min="8" max="8" width="28.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="6" t="s">
         <v>2</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>3</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>7</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">

--- a/report_templates/Payment Status.xlsx
+++ b/report_templates/Payment Status.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3b68409331e52ac1/Documents/GRP/GRP_SYS/report_templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{AF55236C-2425-464B-AFCF-50EEAAF32BAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55E6B1FE-3271-4CED-98AE-DFE3E495A70C}"/>
+  <xr:revisionPtr revIDLastSave="34" documentId="13_ncr:1_{AF55236C-2425-464B-AFCF-50EEAAF32BAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E913950-3F0D-47E0-AAAB-22413E6C9FAB}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>INSTA.</t>
   </si>
@@ -44,9 +44,6 @@
     <t>PAY.STATUS</t>
   </si>
   <si>
-    <t>P.D.C. CHEUQE</t>
-  </si>
-  <si>
     <t>CUSTOMER</t>
   </si>
   <si>
@@ -60,13 +57,22 @@
   </si>
   <si>
     <t>SALES PERSON</t>
+  </si>
+  <si>
+    <t>CHEUQE STATUS</t>
+  </si>
+  <si>
+    <t>INSTA.REMARKS</t>
+  </si>
+  <si>
+    <t>DEL.REMARKS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -78,13 +84,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -131,13 +130,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -428,294 +422,52 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.81640625" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="3" width="11.7265625" customWidth="1"/>
-    <col min="4" max="4" width="11.54296875" customWidth="1"/>
-    <col min="5" max="5" width="11.7265625" customWidth="1"/>
-    <col min="6" max="6" width="14.81640625" customWidth="1"/>
-    <col min="7" max="7" width="15.1796875" customWidth="1"/>
-    <col min="8" max="8" width="28.1796875" customWidth="1"/>
+    <col min="4" max="4" width="20.453125" customWidth="1"/>
+    <col min="5" max="5" width="11.54296875" customWidth="1"/>
+    <col min="6" max="6" width="17" customWidth="1"/>
+    <col min="7" max="7" width="11.7265625" customWidth="1"/>
+    <col min="8" max="8" width="14.81640625" customWidth="1"/>
+    <col min="9" max="9" width="15.1796875" customWidth="1"/>
+    <col min="10" max="10" width="28.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" s="6" t="s">
+      <c r="J1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" s="3"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="2"/>
-      <c r="H2" s="4"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="E3" s="2"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="2"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" s="3"/>
-      <c r="C5" s="1"/>
-      <c r="E5" s="2"/>
-      <c r="H5" s="4"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="2"/>
-      <c r="H6" s="4"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7" s="3"/>
-      <c r="C7" s="1"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A8" s="3"/>
-      <c r="C8" s="1"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A9" s="3"/>
-      <c r="C9" s="1"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A10" s="3"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A11" s="3"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A12" s="3"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="2"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A13" s="3"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A14" s="3"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A15" s="3"/>
-      <c r="C15" s="1"/>
-      <c r="E15" s="2"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17" s="3"/>
-      <c r="C17" s="1"/>
-      <c r="E17" s="2"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A18" s="3"/>
-      <c r="C18" s="1"/>
-      <c r="E18" s="2"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" s="3"/>
-      <c r="C19" s="1"/>
-      <c r="E19" s="2"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A20" s="3"/>
-      <c r="C20" s="1"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" s="3"/>
-      <c r="C21" s="5"/>
-      <c r="E21" s="2"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A22" s="3"/>
-      <c r="C22" s="5"/>
-      <c r="E22" s="2"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23" s="3"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="2"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24" s="3"/>
-      <c r="C24" s="5"/>
-      <c r="E24" s="2"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A25" s="3"/>
-      <c r="C25" s="5"/>
-      <c r="E25" s="2"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26" s="3"/>
-      <c r="C26" s="5"/>
-      <c r="E26" s="2"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A27" s="3"/>
-      <c r="C27" s="5"/>
-      <c r="E27" s="2"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A28" s="3"/>
-      <c r="C28" s="5"/>
-      <c r="E28" s="2"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A29" s="3"/>
-      <c r="C29" s="5"/>
-      <c r="E29" s="2"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A30" s="3"/>
-      <c r="C30" s="5"/>
-      <c r="E30" s="2"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A31" s="3"/>
-      <c r="C31" s="5"/>
-      <c r="E31" s="2"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A32" s="3"/>
-      <c r="C32" s="5"/>
-      <c r="E32" s="2"/>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A33" s="3"/>
-      <c r="C33" s="5"/>
-      <c r="E33" s="2"/>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A34" s="3"/>
-      <c r="C34" s="5"/>
-      <c r="E34" s="2"/>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A35" s="3"/>
-      <c r="C35" s="5"/>
-      <c r="D35" s="3"/>
-      <c r="E35" s="2"/>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A36" s="3"/>
-      <c r="C36" s="5"/>
-      <c r="E36" s="2"/>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A37" s="3"/>
-      <c r="C37" s="5"/>
-      <c r="E37" s="2"/>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A38" s="3"/>
-      <c r="C38" s="5"/>
-      <c r="E38" s="2"/>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A39" s="3"/>
-      <c r="C39" s="5"/>
-      <c r="E39" s="2"/>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A40" s="3"/>
-      <c r="C40" s="5"/>
-      <c r="E40" s="2"/>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A41" s="3"/>
-      <c r="C41" s="5"/>
-      <c r="E41" s="2"/>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A42" s="3"/>
-      <c r="C42" s="5"/>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A43" s="3"/>
-      <c r="C43" s="5"/>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A44" s="3"/>
-      <c r="C44" s="5"/>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A45" s="3"/>
-      <c r="C45" s="5"/>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A46" s="3"/>
-      <c r="C46" s="5"/>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A47" s="3"/>
-      <c r="C47" s="5"/>
-      <c r="D47" s="5"/>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A48" s="3"/>
-      <c r="C48" s="5"/>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A49" s="3"/>
-      <c r="C49" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
